--- a/suppliers_us/Aldera_sachet_packers_2026-10-29.xlsx
+++ b/suppliers_us/Aldera_sachet_packers_2026-10-29.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Есть: производство и фасовка, 1451 Highway 20 West, McDonough</t>
+          <t>Есть, но только как Packaging Facility (фасовка), не производство</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Звонить первым: капсулы и пакетики в одних руках. Уточнить, есть ли в каталоге магний бисглицинат и ашваганда</t>
+          <t>Звонить первым: капсулы и пакетики в одних руках. Уточнить, есть ли в каталоге магний бисглицинат и ашваганда | ПОПРАВКА 29.10: в реестре NSF Vitalabs записан как Packaging Facility (фасовка и маркировка), без инкапсуляции; капсулы закупают у других (коды bulk-источников HS-MBG01, HS-CO01, см. QUOTES_RAW 02.10). Страна происхождения капсул неизвестна.</t>
         </is>
       </c>
     </row>
